--- a/src/test/resources/LoginTest.xlsx
+++ b/src/test/resources/LoginTest.xlsx
@@ -4,12 +4,16 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13140" windowHeight="4485" activeTab="2"/>
+    <workbookView windowWidth="20490" windowHeight="7620" firstSheet="1" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="New XLS Worksheet" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
+    <sheet name="products" sheetId="4" r:id="rId4"/>
+    <sheet name="cart" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet5" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet6" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +33,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="62">
+  <si>
+    <t>TestMethodName</t>
+  </si>
   <si>
     <t>Username</t>
   </si>
@@ -40,6 +47,9 @@
     <t>Result</t>
   </si>
   <si>
+    <t>loginValidation</t>
+  </si>
+  <si>
     <t>standard_user</t>
   </si>
   <si>
@@ -79,6 +89,9 @@
     <t>result</t>
   </si>
   <si>
+    <t>checkOutTest</t>
+  </si>
+  <si>
     <t>yamini</t>
   </si>
   <si>
@@ -92,6 +105,120 @@
   </si>
   <si>
     <t>pinError</t>
+  </si>
+  <si>
+    <t>ProductList</t>
+  </si>
+  <si>
+    <t>ProductNames</t>
+  </si>
+  <si>
+    <t>ValidateTitle</t>
+  </si>
+  <si>
+    <t>titleName</t>
+  </si>
+  <si>
+    <t>Swag Labs</t>
+  </si>
+  <si>
+    <t>ValidateLabel</t>
+  </si>
+  <si>
+    <t>labelName</t>
+  </si>
+  <si>
+    <t>Products</t>
+  </si>
+  <si>
+    <t>ValidateProduct</t>
+  </si>
+  <si>
+    <t>productName</t>
+  </si>
+  <si>
+    <t>Sauce Labs Backpack</t>
+  </si>
+  <si>
+    <t>ValidateFilterDec</t>
+  </si>
+  <si>
+    <t>prdouctDecending</t>
+  </si>
+  <si>
+    <t>Test.allTheThings() T-Shirt (Red)</t>
+  </si>
+  <si>
+    <t>ValidateFilterAsc</t>
+  </si>
+  <si>
+    <t>productAscending</t>
+  </si>
+  <si>
+    <t>ValidateFilterLtoH</t>
+  </si>
+  <si>
+    <t>lowToHighPrice</t>
+  </si>
+  <si>
+    <t>ValidateFilterHtoL</t>
+  </si>
+  <si>
+    <t>highToLowPrice</t>
+  </si>
+  <si>
+    <t>CartList</t>
+  </si>
+  <si>
+    <t>CartNames</t>
+  </si>
+  <si>
+    <t>ValidateCartLabel</t>
+  </si>
+  <si>
+    <t>cartName</t>
+  </si>
+  <si>
+    <t>Your Cart</t>
+  </si>
+  <si>
+    <t>ValidateCartQty</t>
+  </si>
+  <si>
+    <t>cartQty</t>
+  </si>
+  <si>
+    <t>ValidateCartRemove</t>
+  </si>
+  <si>
+    <t>removeCart</t>
+  </si>
+  <si>
+    <t>Remove</t>
+  </si>
+  <si>
+    <t>ValidateCartPdt</t>
+  </si>
+  <si>
+    <t>cartProduct</t>
+  </si>
+  <si>
+    <t>ValidateCartCheckout</t>
+  </si>
+  <si>
+    <t>cartCheckout</t>
+  </si>
+  <si>
+    <t>Checkout</t>
+  </si>
+  <si>
+    <t>ValidateCartContinue</t>
+  </si>
+  <si>
+    <t>cartContinueShop</t>
+  </si>
+  <si>
+    <t>Continue Shopping</t>
   </si>
 </sst>
 </file>
@@ -104,13 +231,19 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF2A00FF"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -577,138 +710,141 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1260,17 +1396,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="2"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="16.5714285714286" customWidth="1"/>
-    <col min="3" max="3" width="3.28571428571429" customWidth="1"/>
+    <col min="1" max="1" width="25.8571428571429" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="15.8571428571429" customWidth="1"/>
     <col min="4" max="4" width="18.2857142857143" customWidth="1"/>
     <col min="5" max="5" width="16.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1280,71 +1416,92 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
       <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
       <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
         <v>4</v>
       </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1356,71 +1513,323 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="4" outlineLevelCol="3"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="4" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="20.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="19.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="18.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="15.4285714285714" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2">
         <v>500090</v>
       </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <v>500090</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>500090</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="7" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="18.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="31.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="20.2857142857143" customWidth="1"/>
+    <col min="5" max="5" width="16.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="14.7142857142857" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8">
+        <v>49.99</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="21.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="20.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="19.4285714285714" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
       </c>
       <c r="C3">
-        <v>500090</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4"/>
-      <c r="C4">
-        <v>500090</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>51</v>
+      </c>
+      <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5"/>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A2"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="1"/>
+  <sheetData>
+    <row r="2" ht="15.75" spans="1:1">
+      <c r="A2" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A2"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="1"/>
+  <sheetData>
+    <row r="2" ht="15.75" spans="1:1">
+      <c r="A2" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
